--- a/data/trans_dic/P57GLOBAL_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P57GLOBAL_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,73; 73,14</t>
+          <t>64,17; 73,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,88; 72,04</t>
+          <t>62,65; 71,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74,85; 82,65</t>
+          <t>75,02; 83,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,72; 62,75</t>
+          <t>53,76; 62,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,36; 72,22</t>
+          <t>61,73; 72,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,63; 75,8</t>
+          <t>64,47; 75,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,04; 84,57</t>
+          <t>76,25; 84,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,79; 57,96</t>
+          <t>49,87; 57,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64,89; 71,38</t>
+          <t>64,54; 71,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65,13; 72,58</t>
+          <t>65,07; 72,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76,64; 82,72</t>
+          <t>76,66; 82,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,08; 59,14</t>
+          <t>52,88; 59,26</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,28; 70,0</t>
+          <t>59,4; 69,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,74; 72,56</t>
+          <t>62,87; 72,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,71; 81,34</t>
+          <t>72,42; 81,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,31; 69,07</t>
+          <t>59,26; 68,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,09; 72,52</t>
+          <t>63,2; 72,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,14; 78,27</t>
+          <t>67,97; 78,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,2; 84,02</t>
+          <t>75,27; 84,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,01; 68,94</t>
+          <t>59,88; 68,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62,54; 69,49</t>
+          <t>62,55; 69,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,81; 73,69</t>
+          <t>66,98; 74,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75,35; 81,68</t>
+          <t>75,67; 81,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,88; 67,37</t>
+          <t>60,87; 67,57</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,91; 78,86</t>
+          <t>70,87; 78,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,34; 71,96</t>
+          <t>64,16; 71,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,08; 89,28</t>
+          <t>83,33; 89,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,67; 66,37</t>
+          <t>16,08; 66,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,41; 78,0</t>
+          <t>64,54; 78,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,57; 78,02</t>
+          <t>67,02; 78,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,73; 92,52</t>
+          <t>81,21; 92,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61,85; 73,51</t>
+          <t>61,69; 73,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,78; 77,27</t>
+          <t>70,68; 77,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66,37; 72,58</t>
+          <t>66,43; 72,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84,4; 89,25</t>
+          <t>83,94; 89,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,62; 67,27</t>
+          <t>18,84; 67,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,41; 75,39</t>
+          <t>70,24; 75,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,36; 73,18</t>
+          <t>67,23; 72,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,92; 84,46</t>
+          <t>79,73; 84,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,99; 68,64</t>
+          <t>62,14; 68,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,33; 77,88</t>
+          <t>70,81; 77,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,25; 82,62</t>
+          <t>76,78; 82,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,34; 88,1</t>
+          <t>83,24; 88,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>60,29; 66,24</t>
+          <t>60,14; 66,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71,24; 75,4</t>
+          <t>71,59; 75,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71,72; 75,81</t>
+          <t>72,17; 76,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81,94; 85,31</t>
+          <t>81,81; 85,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,16; 66,74</t>
+          <t>62,26; 66,68</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,76; 76,41</t>
+          <t>66,88; 76,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,62; 76,53</t>
+          <t>68,5; 76,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,0; 86,42</t>
+          <t>80,13; 86,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,91; 73,93</t>
+          <t>64,72; 73,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>76,05; 82,64</t>
+          <t>76,05; 82,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,92; 80,25</t>
+          <t>73,79; 80,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,45; 89,49</t>
+          <t>84,61; 89,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45,7; 71,03</t>
+          <t>48,29; 70,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73,69; 79,37</t>
+          <t>73,67; 79,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72,93; 77,81</t>
+          <t>72,89; 77,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83,7; 87,35</t>
+          <t>83,49; 87,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,98; 70,69</t>
+          <t>52,33; 70,3</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54,77; 65,1</t>
+          <t>54,34; 65,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54,91; 66,94</t>
+          <t>55,04; 66,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,91; 83,68</t>
+          <t>73,54; 83,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,67; 56,32</t>
+          <t>34,67; 56,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67,76; 72,95</t>
+          <t>67,9; 72,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,5; 75,67</t>
+          <t>70,76; 75,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,58; 86,92</t>
+          <t>82,33; 86,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61,11; 67,91</t>
+          <t>60,7; 67,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66,02; 70,62</t>
+          <t>65,97; 70,92</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68,41; 73,26</t>
+          <t>68,55; 73,44</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>81,44; 85,56</t>
+          <t>81,63; 85,53</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>56,03; 63,74</t>
+          <t>55,67; 63,72</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>68,71; 72,0</t>
+          <t>68,7; 72,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>67,03; 70,6</t>
+          <t>67,25; 70,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80,51; 83,23</t>
+          <t>80,46; 83,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44,4; 63,74</t>
+          <t>41,61; 63,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,66; 73,83</t>
+          <t>70,75; 73,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,91; 76,95</t>
+          <t>73,85; 76,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,63; 85,92</t>
+          <t>83,4; 85,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>57,34; 64,83</t>
+          <t>57,1; 64,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>70,23; 72,49</t>
+          <t>70,21; 72,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71,09; 73,27</t>
+          <t>71,08; 73,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82,45; 84,3</t>
+          <t>82,44; 84,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,56; 63,47</t>
+          <t>51,44; 63,36</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>304841; 344432</t>
+          <t>302186; 343880</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>273692; 313571</t>
+          <t>272711; 313118</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>320548; 353949</t>
+          <t>321259; 356903</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266582; 311429</t>
+          <t>266824; 312572</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>187465; 220654</t>
+          <t>188598; 222033</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>200417; 235051</t>
+          <t>199919; 234814</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>259636; 288770</t>
+          <t>260348; 289459</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>220761; 257005</t>
+          <t>221106; 256406</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>503834; 554212</t>
+          <t>501166; 556156</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>485419; 540946</t>
+          <t>485034; 540019</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>589883; 636664</t>
+          <t>590017; 636139</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>498818; 555744</t>
+          <t>496873; 556838</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>216596; 255759</t>
+          <t>217030; 254214</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>260713; 301532</t>
+          <t>261289; 301140</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>271266; 303476</t>
+          <t>270213; 303873</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>265294; 308976</t>
+          <t>265104; 307439</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>234619; 269667</t>
+          <t>235010; 270413</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>227809; 261706</t>
+          <t>227255; 262791</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>275769; 308132</t>
+          <t>276015; 308232</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>226381; 260048</t>
+          <t>225881; 259355</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>461105; 512306</t>
+          <t>461117; 515432</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>501061; 552658</t>
+          <t>502275; 555973</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>557419; 604267</t>
+          <t>559836; 605097</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>501954; 555518</t>
+          <t>501882; 557149</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>384002; 427043</t>
+          <t>383806; 424691</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>400123; 447510</t>
+          <t>399021; 447667</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>432807; 465084</t>
+          <t>434083; 466674</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>110260; 439104</t>
+          <t>106364; 437978</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>107434; 130102</t>
+          <t>107653; 130234</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>172541; 202221</t>
+          <t>173701; 202709</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>132878; 150422</t>
+          <t>132042; 150284</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>101433; 120567</t>
+          <t>101176; 119753</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>501357; 547307</t>
+          <t>500671; 545941</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>584804; 639542</t>
+          <t>585348; 639037</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>576881; 610044</t>
+          <t>573742; 609639</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>170261; 555366</t>
+          <t>155507; 556159</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>871915; 933639</t>
+          <t>869866; 931486</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>770179; 836653</t>
+          <t>768666; 834519</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>908337; 959908</t>
+          <t>906114; 956882</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>634948; 703029</t>
+          <t>636498; 704632</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>509512; 556318</t>
+          <t>505815; 554093</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>580082; 628526</t>
+          <t>584090; 627652</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>682805; 721743</t>
+          <t>681973; 722480</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>457497; 502632</t>
+          <t>456363; 502582</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1391052; 1472344</t>
+          <t>1397961; 1474442</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1365557; 1443468</t>
+          <t>1374194; 1448636</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1602537; 1668526</t>
+          <t>1600038; 1666387</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1108349; 1190147</t>
+          <t>1110272; 1188960</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>234040; 267849</t>
+          <t>234437; 267949</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>343381; 382954</t>
+          <t>342785; 383055</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>491523; 530939</t>
+          <t>492302; 530005</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>301616; 343537</t>
+          <t>300755; 342785</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>431775; 469219</t>
+          <t>431794; 468255</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>556036; 603645</t>
+          <t>555088; 602690</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>617599; 654489</t>
+          <t>618802; 655283</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>377033; 585954</t>
+          <t>398388; 583917</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>676737; 728863</t>
+          <t>676528; 729652</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>913570; 974645</t>
+          <t>912990; 974894</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1126402; 1175545</t>
+          <t>1123581; 1175800</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>683227; 911682</t>
+          <t>674833; 906582</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>162861; 193594</t>
+          <t>161586; 195527</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>145507; 177387</t>
+          <t>145858; 177175</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>211527; 239486</t>
+          <t>210466; 238591</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82465; 133970</t>
+          <t>82477; 133873</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>846174; 910999</t>
+          <t>847938; 910027</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>774834; 831657</t>
+          <t>777702; 832763</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>887293; 933951</t>
+          <t>884547; 931765</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>453101; 503477</t>
+          <t>450015; 501633</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1020756; 1091822</t>
+          <t>1019977; 1096488</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>933244; 999348</t>
+          <t>935052; 1001783</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1108102; 1164146</t>
+          <t>1110703; 1163815</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>548695; 624158</t>
+          <t>545151; 623968</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2242634; 2350022</t>
+          <t>2242352; 2352920</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2266449; 2387355</t>
+          <t>2273941; 2387889</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2704659; 2795957</t>
+          <t>2702866; 2793247</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1479551; 2123840</t>
+          <t>1386556; 2120645</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2384857; 2491844</t>
+          <t>2387928; 2491068</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2598414; 2705402</t>
+          <t>2596197; 2700480</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2923447; 3003523</t>
+          <t>2915562; 3004084</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1897948; 2145835</t>
+          <t>1890062; 2140009</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4662927; 4812851</t>
+          <t>4661021; 4807410</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4903252; 5053569</t>
+          <t>4902803; 5056820</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5651885; 5778685</t>
+          <t>5651621; 5775713</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3424810; 4215593</t>
+          <t>3416545; 4208066</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57GLOBAL_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P57GLOBAL_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>57,29%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,17; 73,02</t>
+          <t>64,33; 73,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,65; 71,93</t>
+          <t>63,01; 72,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,02; 83,34</t>
+          <t>75,22; 83,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,76; 62,98</t>
+          <t>54,65; 63,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,73; 72,67</t>
+          <t>61,08; 71,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,47; 75,73</t>
+          <t>64,1; 75,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,25; 84,77</t>
+          <t>75,82; 84,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,87; 57,83</t>
+          <t>50,23; 58,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64,54; 71,63</t>
+          <t>64,64; 71,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65,07; 72,45</t>
+          <t>65,12; 72,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76,66; 82,65</t>
+          <t>76,78; 82,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,88; 59,26</t>
+          <t>54,34; 60,54</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,4; 69,57</t>
+          <t>58,41; 69,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,87; 72,46</t>
+          <t>62,45; 72,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,42; 81,45</t>
+          <t>72,7; 81,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,26; 68,73</t>
+          <t>61,31; 70,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,2; 72,72</t>
+          <t>62,97; 72,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,97; 78,6</t>
+          <t>68,4; 77,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,27; 84,05</t>
+          <t>76,16; 84,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,88; 68,75</t>
+          <t>59,66; 68,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62,55; 69,91</t>
+          <t>62,77; 69,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,98; 74,14</t>
+          <t>66,64; 73,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75,67; 81,79</t>
+          <t>75,42; 81,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,87; 67,57</t>
+          <t>61,87; 68,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,87; 78,42</t>
+          <t>70,37; 78,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,16; 71,98</t>
+          <t>64,45; 72,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,33; 89,58</t>
+          <t>83,23; 89,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,08; 66,2</t>
+          <t>60,04; 69,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,54; 78,08</t>
+          <t>64,84; 78,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,02; 78,21</t>
+          <t>66,52; 78,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,21; 92,43</t>
+          <t>81,08; 92,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61,69; 73,02</t>
+          <t>59,68; 71,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,68; 77,07</t>
+          <t>70,46; 77,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66,43; 72,53</t>
+          <t>66,56; 72,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83,94; 89,19</t>
+          <t>84,21; 89,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,84; 67,37</t>
+          <t>61,51; 68,74</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>65,63%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,24; 75,22</t>
+          <t>70,21; 75,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,23; 72,99</t>
+          <t>67,4; 72,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,73; 84,19</t>
+          <t>79,8; 84,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62,14; 68,79</t>
+          <t>63,17; 69,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,81; 77,57</t>
+          <t>71,14; 77,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,78; 82,51</t>
+          <t>76,7; 82,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,24; 88,19</t>
+          <t>83,45; 87,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>60,14; 66,23</t>
+          <t>61,86; 67,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71,59; 75,51</t>
+          <t>71,51; 75,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72,17; 76,08</t>
+          <t>71,91; 75,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81,81; 85,2</t>
+          <t>81,91; 85,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,26; 66,68</t>
+          <t>63,41; 67,7</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>71,27%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,88; 76,44</t>
+          <t>66,59; 76,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,5; 76,55</t>
+          <t>68,89; 76,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,13; 86,27</t>
+          <t>80,31; 86,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,72; 73,77</t>
+          <t>65,4; 74,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>76,05; 82,47</t>
+          <t>76,01; 82,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,79; 80,12</t>
+          <t>73,84; 80,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,61; 89,6</t>
+          <t>84,46; 89,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>48,29; 70,78</t>
+          <t>69,45; 74,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73,67; 79,46</t>
+          <t>73,83; 79,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72,89; 77,83</t>
+          <t>72,9; 77,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83,49; 87,37</t>
+          <t>83,52; 87,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,33; 70,3</t>
+          <t>69,12; 74,02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54,34; 65,75</t>
+          <t>54,0; 65,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,04; 66,86</t>
+          <t>55,49; 67,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,54; 83,37</t>
+          <t>74,23; 83,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,67; 56,28</t>
+          <t>37,9; 57,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67,9; 72,87</t>
+          <t>67,66; 72,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,76; 75,77</t>
+          <t>70,53; 76,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,33; 86,72</t>
+          <t>82,28; 86,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60,7; 67,66</t>
+          <t>62,17; 69,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65,97; 70,92</t>
+          <t>66,06; 70,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68,55; 73,44</t>
+          <t>68,37; 73,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>81,63; 85,53</t>
+          <t>81,61; 85,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>55,67; 63,72</t>
+          <t>58,0; 65,1</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>68,7; 72,08</t>
+          <t>68,86; 71,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>67,25; 70,62</t>
+          <t>67,41; 70,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80,46; 83,15</t>
+          <t>80,5; 83,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41,61; 63,64</t>
+          <t>62,49; 66,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,75; 73,81</t>
+          <t>70,75; 73,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,85; 76,81</t>
+          <t>73,78; 76,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,4; 85,93</t>
+          <t>83,57; 86,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>57,1; 64,66</t>
+          <t>63,88; 66,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>70,21; 72,41</t>
+          <t>70,24; 72,56</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71,08; 73,32</t>
+          <t>71,0; 73,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82,44; 84,25</t>
+          <t>82,32; 84,22</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,44; 63,36</t>
+          <t>63,51; 65,93</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289112</t>
+          <t>321899</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>239022</t>
+          <t>265258</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>528134</t>
+          <t>587157</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>302186; 343880</t>
+          <t>302945; 345365</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>272711; 313118</t>
+          <t>274280; 315605</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>321259; 356903</t>
+          <t>322118; 356483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266824; 312572</t>
+          <t>295963; 344642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>188598; 222033</t>
+          <t>186620; 219883</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>199919; 234814</t>
+          <t>198750; 233454</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>260348; 289459</t>
+          <t>258880; 287697</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>221106; 256406</t>
+          <t>242768; 283931</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>501166; 556156</t>
+          <t>501939; 553048</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>485034; 540019</t>
+          <t>485383; 537559</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>590017; 636139</t>
+          <t>590976; 635660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>496873; 556838</t>
+          <t>556921; 620508</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>287648</t>
+          <t>314693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>243220</t>
+          <t>267249</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>530867</t>
+          <t>581942</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>217030; 254214</t>
+          <t>213414; 255123</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>261289; 301140</t>
+          <t>259508; 301401</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>270213; 303873</t>
+          <t>271249; 303667</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>265104; 307439</t>
+          <t>293198; 335788</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>235010; 270413</t>
+          <t>234167; 269960</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>227255; 262791</t>
+          <t>228697; 260423</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>276015; 308232</t>
+          <t>279292; 310254</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>225881; 259355</t>
+          <t>248839; 284563</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>461117; 515432</t>
+          <t>462749; 515692</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>502275; 555973</t>
+          <t>499780; 553185</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>559836; 605097</t>
+          <t>557975; 604527</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>501882; 557149</t>
+          <t>553920; 612470</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271813</t>
+          <t>301406</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>111031</t>
+          <t>122540</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>382845</t>
+          <t>423945</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>383806; 424691</t>
+          <t>381105; 422528</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>399021; 447667</t>
+          <t>400850; 448535</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>434083; 466674</t>
+          <t>433603; 464117</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106364; 437978</t>
+          <t>278398; 322277</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>107653; 130234</t>
+          <t>108147; 130210</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>173701; 202709</t>
+          <t>172402; 202482</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>132042; 150284</t>
+          <t>131827; 150049</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>101176; 119753</t>
+          <t>110020; 132482</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>500671; 545941</t>
+          <t>499117; 547609</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>585348; 639037</t>
+          <t>586456; 642347</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>573742; 609639</t>
+          <t>575577; 610674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>155507; 556159</t>
+          <t>398654; 445507</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>668244</t>
+          <t>742478</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>480489</t>
+          <t>547749</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1148733</t>
+          <t>1290226</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>869866; 931486</t>
+          <t>869423; 931524</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>768666; 834519</t>
+          <t>770563; 833122</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>906114; 956882</t>
+          <t>906948; 958199</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>636498; 704632</t>
+          <t>708058; 774779</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>505815; 554093</t>
+          <t>508170; 554842</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>584090; 627652</t>
+          <t>583511; 629235</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>681973; 722480</t>
+          <t>683668; 720916</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>456363; 502582</t>
+          <t>522670; 573518</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1397961; 1474442</t>
+          <t>1396244; 1472504</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1374194; 1448636</t>
+          <t>1369167; 1446043</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1600038; 1666387</t>
+          <t>1601907; 1668805</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1110272; 1188960</t>
+          <t>1246566; 1330866</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>321933</t>
+          <t>388032</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>514451</t>
+          <t>587286</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>836383</t>
+          <t>975318</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>234437; 267949</t>
+          <t>233429; 268069</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>342785; 383055</t>
+          <t>344718; 384529</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>492302; 530005</t>
+          <t>493385; 531564</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>300755; 342785</t>
+          <t>363497; 412984</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>431794; 468255</t>
+          <t>431553; 470703</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>555088; 602690</t>
+          <t>555464; 602651</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>618802; 655283</t>
+          <t>617694; 653716</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>398388; 583917</t>
+          <t>564453; 607994</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>676528; 729652</t>
+          <t>678029; 726824</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>912990; 974894</t>
+          <t>913146; 975811</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1123581; 1175800</t>
+          <t>1123918; 1175219</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>674833; 906582</t>
+          <t>945874; 1012928</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107709</t>
+          <t>112948</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>478682</t>
+          <t>541532</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>586391</t>
+          <t>654479</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>161586; 195527</t>
+          <t>160576; 193561</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>145858; 177175</t>
+          <t>147044; 178739</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>210466; 238591</t>
+          <t>212432; 239834</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82477; 133873</t>
+          <t>88880; 135947</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>847938; 910027</t>
+          <t>844938; 909821</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>777702; 832763</t>
+          <t>775251; 835953</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>884547; 931765</t>
+          <t>884091; 933005</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>450015; 501633</t>
+          <t>513176; 569639</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1019977; 1096488</t>
+          <t>1021379; 1092979</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>935052; 1001783</t>
+          <t>932582; 999957</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1110703; 1163815</t>
+          <t>1110423; 1165016</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>545151; 623968</t>
+          <t>614790; 690026</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1946458</t>
+          <t>2181456</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2066895</t>
+          <t>2331613</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4013353</t>
+          <t>4513069</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2242352; 2352920</t>
+          <t>2247668; 2348736</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2273941; 2387889</t>
+          <t>2279613; 2384811</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2702866; 2793247</t>
+          <t>2704185; 2791141</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1386556; 2120645</t>
+          <t>2121474; 2245411</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2387928; 2491068</t>
+          <t>2387729; 2486086</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2596197; 2700480</t>
+          <t>2594035; 2699864</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2915562; 3004084</t>
+          <t>2921401; 3009090</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1890062; 2140009</t>
+          <t>2279286; 2381587</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4661021; 4807410</t>
+          <t>4663061; 4817526</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4902803; 5056820</t>
+          <t>4897257; 5049647</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5651621; 5775713</t>
+          <t>5643260; 5773439</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3416545; 4208066</t>
+          <t>4421838; 4590841</t>
         </is>
       </c>
     </row>
